--- a/out/M01_mobile_network_experience/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/M01_mobile_network_experience/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
+          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3533,146 +3533,15 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>TC-874504db82</t>
+          <t>TC-4cc526034c</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Q9's wording comes from Q7's answer: the earlier answer should appear in the wording</t>
+          <t>Prove the survey flows correctly at Q10: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>1. Q9's wording includes the words: Dropped calls</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>TC-38d52f5f68</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Q9 shown by its condition while also depending on Q7: both should hold at once</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>At Q9, choose “Yes, fully”, then submit.</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>1. Q9 IS shown on the page
-2. Q9's wording includes the words: Dropped calls</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Two behaviours together</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>TC-4cc526034c</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Prove the survey flows correctly at Q10: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3694,58 +3563,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>1. Q10 IS shown on the page
 2. the next question shown is Q11</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>TC-7a15a8b38e</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 DOES appear when its condition is met. The QRE says show it if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3761,57 +3630,57 @@
 12. Q9 = Yes, fully</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>1. Q10 IS shown on the page</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>TC-6a0b049e44</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 does NOT appear when its condition is not met. The QRE says show it if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3827,58 +3696,58 @@
 12. Q9 = No</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>1. Q10 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>TC-d650e06f3a</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3894,191 +3763,58 @@
 12. Q9 = Yes, fully</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q10</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>TC-710a0bf392</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Q10's wording comes from Q9's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls
-12. Q9 = Yes, fully</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>1. Q10's wording includes the words: Yes, fully</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>TC-053ba604ad</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Q10 shown by its condition while also depending on Q9: both should hold at once</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls
-12. Q9 = Yes, fully</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>At Q10, choose “Very poor”, then submit.</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>1. Q10 IS shown on the page
-2. Q10's wording includes the words: Yes, fully</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Two behaviours together</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>TC-2655ae8cc0</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q11: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4100,58 +3836,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>1. Q11 IS shown on the page
 2. the next question shown is Q12</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>TC-033467f6e9</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4168,125 +3904,58 @@
 13. Q10 = Very poor</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q11</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Q11</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>TC-00f13c82b5</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>Q11's wording comes from Q1's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls
-12. Q9 = Yes, fully
-13. Q10 = Very poor</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>At Q11, choose “0”, then submit.</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>1. Q11's wording includes the words: Provider A</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>TC-879d805a3e</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q12: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4308,58 +3977,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>1. Q12 IS shown on the page
 2. the next question shown is Q13</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>TC-d0bb219a46</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4377,126 +4046,58 @@
 14. Q11 = 0</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q12</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Q12</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>TC-57ca05ca80</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Q12's wording comes from Q1's answer: the earlier answer should appear in the wording</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls
-11. Q8 = Dropped calls
-12. Q9 = Yes, fully
-13. Q10 = Very poor
-14. Q11 = 0</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>At Q12, choose “Definitely not”, then submit.</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>1. Q12's wording includes the words: Provider A</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Wording carried forward</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>TC-057fbbd3be</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q13: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4518,58 +4119,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>1. Q13 IS shown on the page
 2. the next question shown is DT2</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>TC-3846ddab6f</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4588,58 +4189,58 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q13</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>TC-d971b5487c</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4658,58 +4259,58 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>1. Q13 shows exactly 5 options, none missing and none repeated
 2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>TC-033a7e07d0</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -4729,57 +4330,57 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q13 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>DT2</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>TC-72b21a0117</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at DT2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4801,57 +4402,57 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is D1</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>TC-a8b01845f7</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4873,58 +4474,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>1. D1 IS shown on the page
 2. the next question shown is D2</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>TC-4fe13ff0c5</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4944,58 +4545,58 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D1</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>TC-6bbd35bfde</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'North' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5015,57 +4616,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>TC-a6aa4b46f5</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'South' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5085,57 +4686,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>TC-7c1f8cedf1</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'East' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5155,57 +4756,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>TC-bcc0d47257</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'West' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5225,57 +4826,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>TC-54f03c2ec8</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'Central' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5295,57 +4896,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>TC-5532fdc6f0</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5367,58 +4968,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>1. D2 IS shown on the page
 2. the next question shown is Q14</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>TC-436b2784d3</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5439,59 +5040,59 @@
 17. D1 = North</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D2</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>TC-a072344565</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q14: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5513,59 +5114,59 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>1. Q14 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>TC-a732732d23</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5587,58 +5188,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>TC-8fbc091a4e</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5660,59 +5261,59 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q14</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>TC-d7e0adcd35</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5734,58 +5335,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>TC-ca20214ae3</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5807,58 +5408,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>TC-aec3d7938e</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5880,58 +5481,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>TC-75f0109276</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5953,53 +5554,53 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>TC-46e96b9817</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -6021,22 +5622,22 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/out/M01_mobile_network_experience/agent3/agent3_test_cases_for_review.xlsx
+++ b/out/M01_mobile_network_experience/agent3/agent3_test_cases_for_review.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>TC-8eaedcc803</t>
+          <t>TC-3cdefc3fa7</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Prove S3 ACCEPTS an answer that obeys its rule. The QRE's rule is: the number must be at least 18; the number must be at most 80</t>
+          <t>Prove reject rule R3 does NOT fire. The rule is: S3 &lt; 18 or S3 &gt; 80</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>TC-f2d9cfbc7a</t>
+          <t>TC-8eaedcc803</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Prove S3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a integer question</t>
+          <t>Prove S3 ACCEPTS an answer that obeys its rule. The QRE's rule is: the number must be at least 18; the number must be at most 80  [Same actions as TC-3cdefc3fa7 on this question: the questionnaire's answer rule and its compulsory setting come down to the same thing here. Both are kept because they are separate claims, but one run satisfies both.]</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1043,18 +1043,17 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>At S3, type nothing, then submit.</t>
+          <t>At S3, type “18”, then submit.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against S3</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Blank answer is blocked</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1069,30 +1068,201 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>S3 | What is your age? | integer | — | Validate: {"min": 18, "max": 80}</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>TC-d9eb6b4c72</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Prove reject rule R3 DOES fire. The rule is: S3 &lt; 18 or S3 &gt; 80</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>At S3, type “17”, then submit.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against R3</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>S3 | What is your age? | integer | — | Validate: {"min": 18, "max": 80}</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>TC-d85089896f</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Prove S3 REJECTS an answer that breaks its rule. The QRE's rule is: the number must be at least 18; the number must be at most 80</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>At S3, type “81”, then submit.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against S3</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Answer rule accepts or rejects</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>S3 | What is your age? | integer | — | Validate: {"min": 18, "max": 80}</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>TC-f2d9cfbc7a</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Prove S3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a integer question</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>At S3, type nothing, then submit.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against S3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>DT1</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>DT1 | Great, you're eligible for this survey! Next, a few questions about your recent mobile network experience. | text display | — | Always show</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>TC-f4e1e7e3f0</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at DT1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1114,57 +1284,57 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is Q1</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Q1 | Which mobile network services channel or provider did you use most recently? | single | Provider A; Provider B; Provider C; Provider D | Always show</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>TC-d23422ef01</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1186,116 +1356,116 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>1. Q1 IS shown on the page
 2. the next question shown is Q2</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Q1 | Which mobile network services channel or provider did you use most recently? | single | Provider A; Provider B; Provider C; Provider D | Always show</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>TC-da7f7de89a</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
 3. S3 = 18</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>At Q1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q1</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Q2 | When did the most recent experience occur? | single | Within 7 days; 8-30 days; 1-3 months; 4-6 months | Always show</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>TC-db1b5bbec9</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1317,58 +1487,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>1. Q2 IS shown on the page
 2. the next question shown is Q3</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Q2 | When did the most recent experience occur? | single | Within 7 days; 8-30 days; 1-3 months; 4-6 months | Always show</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>TC-02f3b41b09</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1376,58 +1546,58 @@
 4. Q1 = Provider A</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q2</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>TC-40cf43a650</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q3: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1449,200 +1619,20 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>1. Q3 IS shown on the page
 2. the next question shown is Q4</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>TC-1aa6211d83</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>At Q3, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q3</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>TC-b837190e03</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q3 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>At Q3, choose “Calls”, then submit.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>1. Q3 shows exactly 5 options, none missing and none repeated
-2. the options shown at Q3 are exactly: Calls, Customer support, International roaming, Mobile data, Recharge or billing</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>TC-21a998033c</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q3 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Run this same path 5 times and record the option order each time, then compare them.
-1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>At Q3, choose “Calls”, then submit.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>1. the order the options appear in at Q3 is NOT identical on every run</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Shuffled options</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1657,30 +1647,210 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>TC-1aa6211d83</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>At Q3, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q3</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>TC-b837190e03</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q3 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>At Q3, choose “Calls”, then submit.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>1. Q3 shows exactly 5 options, none missing and none repeated
+2. the options shown at Q3 are exactly: Calls, Customer support, International roaming, Mobile data, Recharge or billing</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Shuffled options</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Q3 | What was the primary purpose of the experience? | single | Calls; Mobile data; Recharge or billing; Customer support; International roaming | Randomize</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>TC-21a998033c</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q3 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Run this same path 5 times and record the option order each time, then compare them.
+1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>At Q3, choose “Calls”, then submit.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>1. the order the options appear in at Q3 is NOT identical on every run</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Shuffled options</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>TC-4f66eed2b0</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q4: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1702,58 +1872,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>1. Q4 IS shown on the page
 2. the next question shown is Q5</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Q4 | Rate your overall satisfaction. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>TC-2bb3a85e2e</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1763,58 +1933,58 @@
 6. Q3 = Calls</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q4</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>TC-8c2e1ee027</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q5: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1836,58 +2006,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>1. Q5 IS shown on the page
 2. the next question shown is Q6</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Q5 | Rate the ease of completing the experience. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>TC-6a0e1c7a69</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1898,58 +2068,58 @@
 7. Q4 = Very poor</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>At Q5, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q5</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>TC-162320a86d</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q6: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -1971,58 +2141,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>1. Q6 IS shown on the page
 2. the next question shown is Q7_SQ001</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Q6 | Rate the clarity of information provided. | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>TC-0a0c06b64a</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2034,59 +2204,59 @@
 8. Q5 = Very poor</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>At Q6, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q6</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Q7</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
 Randomize</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>TC-9b078f9282</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q7: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2108,212 +2278,20 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>1. Q7 IS shown on the page
 2. the next question shown is Q8</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>TC-19974e9af2</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Rule R6: the jump should happen. Jump to Q11 when Q7 == ['None of these']</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>At Q7, tick 1 option (None of these), then submit.</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>1. the next question shown is Q11</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>TC-bcf1edd70a</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Rule R6: the jump should not happen. Jump to Q11 when Q7 == ['None of these']</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>1. the next question shown is Q8</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
-Randomize</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>TC-d869eec605</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q7 ACCEPTS an answer that obeys its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>At Q7, tick 1 option (None of these), then submit.</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2344,12 +2322,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>TC-7e44cb39fa</t>
+          <t>TC-19974e9af2</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R9 does NOT fire. The rule is: Q7 includes 'None of these' plus another option</t>
+          <t>Rule R6: the jump should happen. Jump to Q11 when Q7 == ['None of these']</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2367,17 +2345,17 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>At Q7, tick 1 option (None of these), then submit.</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
+          <t>1. the next question shown is Q11</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Shows / hides correctly</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2408,12 +2386,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>TC-ec044371e9</t>
+          <t>TC-bcf1edd70a</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 REJECTS an answer that breaks its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
+          <t>Rule R6: the jump should not happen. Jump to Q11 when Q7 == ['None of these']</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2431,18 +2409,17 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the next question shown is Q8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Answer rule accepts or rejects</t>
+          <t>Shows / hides correctly</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2473,12 +2450,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>TC-9344abb8c4</t>
+          <t>TC-d869eec605</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Prove reject rule R9 DOES fire. The rule is: Q7 includes 'None of these' plus another option</t>
+          <t>Prove Q7 ACCEPTS an answer that obeys its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2496,13 +2473,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
+          <t>At Q7, tick 1 option (None of these), then submit.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against R9</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2538,12 +2514,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TC-b50e131bc4</t>
+          <t>TC-7e44cb39fa</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question</t>
+          <t>Prove reject rule R9 does NOT fire. The rule is: Q7 includes 'None of these' plus another option</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2561,18 +2537,17 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Blank answer is blocked</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2603,12 +2578,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>TC-25ad3cc4ce</t>
+          <t>TC-ec044371e9</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 still shows all 6 of its options when shuffled, with none dropped and none duplicated</t>
+          <t>Prove Q7 REJECTS an answer that breaks its rule. The QRE's rule is: “None of these” cannot be chosen alongside anything else</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2626,18 +2601,18 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>At Q7, tick 2 options (None of these, Dropped calls), then submit.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>1. Q7 shows exactly 6 options, none missing and none repeated
-2. the options shown at Q7 are exactly: Coverage gap, Dropped calls, None of these, Slow data, Support delay, Unexpected charge</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Shuffled options</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2668,18 +2643,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>TC-dde31580a1</t>
+          <t>TC-9344abb8c4</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Prove Q7 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
+          <t>Prove reject rule R9 DOES fire. The rule is: Q7 includes 'None of these' plus another option</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Run this same path 5 times and record the option order each time, then compare them.
-1. S1 = Yes
+          <t>1. S1 = Yes
 2. S2 = Yes
 3. S3 = 18
 4. Q1 = Provider A
@@ -2692,17 +2666,18 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+          <t>At Q7, tick 2 options (Dropped calls, None of these), then submit.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>1. the order the options appear in at Q7 is NOT identical on every run</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against R9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Shuffled options</t>
+          <t>Answer rule accepts or rejects</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2717,31 +2692,226 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
+Randomize</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>TC-b50e131bc4</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
+Randomize</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>TC-25ad3cc4ce</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q7 still shows all 6 of its options when shuffled, with none dropped and none duplicated</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>1. Q7 shows exactly 6 options, none missing and none repeated
+2. the options shown at Q7 are exactly: Coverage gap, Dropped calls, None of these, Slow data, Support delay, Unexpected charge</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Shuffled options</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | Did you experience any of the following problems? | multi | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay; None of these | Validate: {"exclusive_option": "None of these"}
+Randomize</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TC-dde31580a1</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q7 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Run this same path 5 times and record the option order each time, then compare them.
+1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>At Q7, tick 1 option (Dropped calls), then submit.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>1. the order the options appear in at Q7 is NOT identical on every run</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Shuffled options</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
 Show only options selected at Q7.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>TC-0bd4ceda82</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q8: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -2763,217 +2933,20 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>1. Q8 IS shown on the page
 2. the next question shown is Q9</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>TC-f59fc0072e</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q8 DOES appear when its condition is met. The QRE says show it if: Q7 contains any problem</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>At Q8, choose “Dropped calls”, then submit.</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>1. Q8 IS shown on the page</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>TC-d1eb276152</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q8 does NOT appear when its condition is not met. The QRE says show it if: Q7 contains any problem</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = None of these</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>1. Q8 is NOT shown on the page
-2. the respondent carries on into the survey rather than being screened out or finished</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Shows / hides correctly</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
-Show only options selected at Q7.</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>TC-f4e804fd75</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>1. S1 = Yes
-2. S2 = Yes
-3. S3 = 18
-4. Q1 = Provider A
-5. Q2 = Within 7 days
-6. Q3 = Calls
-7. Q4 = Very poor
-8. Q5 = Very poor
-9. Q6 = Very poor
-10. Q7 = Dropped calls</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>At Q8, select nothing at all, then submit.</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Blank answer is blocked</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3004,12 +2977,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>TC-a23083abc4</t>
+          <t>TC-f59fc0072e</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Q8's option list comes from Q7's answer: the option list should be narrowed</t>
+          <t>Prove Q8 DOES appear when its condition is met. The QRE says show it if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3033,12 +3006,12 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>1. Q8 offers exactly these options and no others: A001</t>
+          <t>1. Q8 IS shown on the page</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Options carried forward</t>
+          <t>Shows / hides correctly</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3069,12 +3042,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>TC-538110a30f</t>
+          <t>TC-d1eb276152</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Q8 shown by its condition while also depending on Q7: both should hold at once</t>
+          <t>Prove Q8 does NOT appear when its condition is not met. The QRE says show it if: Q7 contains any problem</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3088,23 +3061,23 @@
 7. Q4 = Very poor
 8. Q5 = Very poor
 9. Q6 = Very poor
-10. Q7 = Dropped calls</t>
+10. Q7 = None of these</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>At Q8, choose “Dropped calls”, then submit.</t>
+          <t>After submitting Q7, look for Q8 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>1. Q8 IS shown on the page
-2. Q8's wording includes the words: Dropped calls</t>
+          <t>1. Q8 is NOT shown on the page
+2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Two behaviours together</t>
+          <t>Shows / hides correctly</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3119,30 +3092,227 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
+Show only options selected at Q7.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>TC-f4e804fd75</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Prove Q8 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor
+10. Q7 = Dropped calls</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>At Q8, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Blank answer is blocked</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
+Show only options selected at Q7.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>TC-a23083abc4</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Q8's option list comes from Q7's answer: the option list should be narrowed</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor
+10. Q7 = Dropped calls</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>At Q8, choose “Dropped calls”, then submit.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>1. Q8 offers exactly these options and no others: A001</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Options carried forward</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Q8 | Which problem had the greatest impact? | single | Dropped calls; Slow data; Unexpected charge; Coverage gap; Support delay | Show if: Q7 contains any problem
+Show only options selected at Q7.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>TC-538110a30f</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Q8 shown by its condition while also depending on Q7: both should hold at once</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>1. S1 = Yes
+2. S2 = Yes
+3. S3 = 18
+4. Q1 = Provider A
+5. Q2 = Within 7 days
+6. Q3 = Calls
+7. Q4 = Very poor
+8. Q5 = Very poor
+9. Q6 = Very poor
+10. Q7 = Dropped calls</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>At Q8, choose “Dropped calls”, then submit.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>1. Q8 IS shown on the page
+2. Q8's wording includes the words: Dropped calls</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Two behaviours together</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>TC-6bcc316c93</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q9: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3164,58 +3334,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>1. Q9 IS shown on the page
 2. the next question shown is Q10</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>TC-ce138104b4</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Prove Q9 DOES appear when its condition is met. The QRE says show it if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3230,57 +3400,57 @@
 11. Q8 = Dropped calls</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>1. Q9 IS shown on the page</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>TC-6da391caf2</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Prove Q9 does NOT appear when its condition is not met. The QRE says show it if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3294,58 +3464,58 @@
 10. Q7 = None of these</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>After submitting Q7, look for Q9 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>1. Q9 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>TC-2413678ad4</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Rule R8: the jump should happen. Jump to Q11 when Q9 == 'No'</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3360,57 +3530,57 @@
 11. Q8 = Dropped calls</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>At Q9, choose “No”, then submit.</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is Q11</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>TC-130c5f812d</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Rule R8: the jump should not happen. Jump to Q11 when Q9 == 'No'</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3425,57 +3595,57 @@
 11. Q8 = Dropped calls</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>At Q9, choose “Yes, fully”, then submit.</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is Q10</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Q9 | Was the main problem resolved? | single | Yes, fully; Yes, partly; No | Show if: Q7 contains any problem</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>TC-55ed8051d0</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>Prove Q9 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3490,58 +3660,58 @@
 11. Q8 = Dropped calls</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>At Q9, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q9</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>TC-4cc526034c</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q10: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3563,58 +3733,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>1. Q10 IS shown on the page
 2. the next question shown is Q11</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>TC-7a15a8b38e</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 DOES appear when its condition is met. The QRE says show it if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3630,57 +3800,57 @@
 12. Q9 = Yes, fully</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>At Q10, choose “Very poor”, then submit.</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>1. Q10 IS shown on the page</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>TC-6a0b049e44</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 does NOT appear when its condition is not met. The QRE says show it if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3696,58 +3866,58 @@
 12. Q9 = No</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>After submitting Q9, look for Q10 on the next page. Do not answer it.</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>1. Q10 is NOT shown on the page
 2. the respondent carries on into the survey rather than being screened out or finished</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Q10 | How satisfied were you with the resolution? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Show if: Q9 in ['Yes, fully','Yes, partly']</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>TC-d650e06f3a</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Prove Q10 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3763,58 +3933,58 @@
 12. Q9 = Yes, fully</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>At Q10, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q10</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>TC-2655ae8cc0</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q11: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3836,58 +4006,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>1. Q11 IS shown on the page
 2. the next question shown is Q12</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Q11 | How likely are you to recommend the provider? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>TC-033467f6e9</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Prove Q11 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3904,58 +4074,58 @@
 13. Q10 = Very poor</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>At Q11, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q11</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>TC-879d805a3e</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q12: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -3977,58 +4147,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>1. Q12 IS shown on the page
 2. the next question shown is Q13</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Q12 | How likely are you to continue using the provider? | single | Definitely not; Probably not; Unsure; Probably; Definitely | Always show</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>TC-d0bb219a46</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>Prove Q12 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4046,58 +4216,58 @@
 14. Q11 = 0</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>At Q12, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q12</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>TC-057fbbd3be</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q13: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4119,58 +4289,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>1. Q13 IS shown on the page
 2. the next question shown is DT2</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>TC-3846ddab6f</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4189,58 +4359,58 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>At Q13, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q13</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>TC-d971b5487c</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 still shows all 5 of its options when shuffled, with none dropped and none duplicated</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4259,58 +4429,58 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>1. Q13 shows exactly 5 options, none missing and none repeated
 2. the options shown at Q13 are exactly: Better staff support, Clearer information, Faster service, Improved digital experience, Lower cost</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Q13 | Which improvement would have the greatest value? | single | Lower cost; Faster service; Clearer information; Better staff support; Improved digital experience | Randomize</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>TC-033a7e07d0</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>Prove Q13 is actually shuffled: the option order must differ between respondents. If it never changes, shuffling was not switched on</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>Run this same path 5 times and record the option order each time, then compare them.
 1. S1 = Yes
@@ -4330,57 +4500,57 @@
 15. Q12 = Definitely not</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>At Q13, choose “Lower cost”, then submit.</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>1. the order the options appear in at Q13 is NOT identical on every run</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Shuffled options</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>DT2</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>DT2 | You're almost done! Thank you for your answers. Just a few last questions about you to finish up. | text display | — | Always show</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>TC-72b21a0117</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at DT2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4402,57 +4572,57 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>1. the next question shown is D1</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>TC-a8b01845f7</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D1: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4474,58 +4644,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>1. D1 IS shown on the page
 2. the next question shown is D2</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>TC-4fe13ff0c5</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>Prove D1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4545,58 +4715,58 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>At D1, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D1</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>TC-6bbd35bfde</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'North' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4616,57 +4786,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “North”, then submit.</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>TC-a6aa4b46f5</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'South' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4686,57 +4856,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “South”, then submit.</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>TC-7c1f8cedf1</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'East' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4756,57 +4926,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “East”, then submit.</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>TC-bcc0d47257</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'West' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4826,57 +4996,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “West”, then submit.</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>D1 | Which region do you live in? | single | North; South; East; West; Central | Always show</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>TC-54f03c2ec8</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>Prove quota QUOTA_REGION lets a 'Central' respondent through while that group is still below its target</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4896,57 +5066,57 @@
 16. Q13 = Lower cost</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>At D1, choose “Central”, then submit.</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>1. the respondent is allowed to continue, not sent to the quota-full ending</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Quota accepts or turns away</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>TC-5532fdc6f0</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at D2: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -4968,58 +5138,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>1. D2 IS shown on the page
 2. the next question shown is Q14</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>D2 | Which age group describes you? | single | 18-24; 25-34; 35-44; 45-54; 55+ | Always show</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>TC-436b2784d3</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Prove D2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5040,59 +5210,59 @@
 17. D1 = North</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>At D2, select nothing at all, then submit.</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against D2</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>TC-a072344565</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Prove the survey flows correctly at Q14: answer it normally and the respondent should move on to whatever the questionnaire says comes next, not stop or jump elsewhere</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5114,59 +5284,59 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>1. Q14 IS shown on the page
 2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Shows / hides correctly</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>TC-a732732d23</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 ACCEPTS an answer that obeys its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5188,58 +5358,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “x”, then submit.</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>TC-8fbc091a4e</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5261,59 +5431,59 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 751-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
 2. an error message is shown against Q14</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>TC-d7e0adcd35</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 lets the respondent through with no answer, because the questionnaire marks it optional</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5335,58 +5505,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>At Q14, type nothing, then submit.</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>TC-ca20214ae3</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5408,58 +5578,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>At Q14, type a 750-character answer, then submit.</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>TC-aec3d7938e</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 REJECTS an answer that breaks its rule. The QRE's rule is: the answer must be at most 750 characters</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5481,58 +5651,58 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>At Q14, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Answer rule accepts or rejects</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Q14 | Please provide any final comments. | text | — | Validate: {"max_length": 750}
 Optional</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>TC-75f0109276</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>Prove Q14 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5554,53 +5724,53 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>At Q14, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>1. the survey ACCEPTS the answer and moves to the next page</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Blank answer is blocked</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>TC-46e96b9817</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>Prove the survey finishes normally for a respondent who answers everything and triggers no screen-out</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>1. S1 = Yes
 2. S2 = Yes
@@ -5622,22 +5792,22 @@
 18. D2 = 18-24</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Survey ends in the right place</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
